--- a/lab/ornek/trade-analytics-sample-result.xlsx
+++ b/lab/ornek/trade-analytics-sample-result.xlsx
@@ -89,7 +89,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYNTHETIC SAMPLE. Not real data, not investment advice. Generated by Kalibre Markets.</t>
+          <t xml:space="preserve">Example.</t>
         </is>
       </c>
     </row>
